--- a/artfynd/A 58169-2023 artfynd.xlsx
+++ b/artfynd/A 58169-2023 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354089</v>
+        <v>121354501</v>
       </c>
       <c r="B4" t="n">
-        <v>79216</v>
+        <v>57364</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,26 +903,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,7 +946,7 @@
         <v>571517</v>
       </c>
       <c r="R4" t="n">
-        <v>6450391</v>
+        <v>6450430</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +987,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354069</v>
+        <v>121354089</v>
       </c>
       <c r="B5" t="n">
-        <v>78243</v>
+        <v>79216</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571526</v>
+        <v>571517</v>
       </c>
       <c r="R5" t="n">
-        <v>6450419</v>
+        <v>6450391</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354501</v>
+        <v>121354069</v>
       </c>
       <c r="B6" t="n">
-        <v>57364</v>
+        <v>78243</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,39 +1127,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571517</v>
+        <v>571526</v>
       </c>
       <c r="R6" t="n">
-        <v>6450430</v>
+        <v>6450419</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,6 +1198,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58169-2023 artfynd.xlsx
+++ b/artfynd/A 58169-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121354996</v>
       </c>
       <c r="B2" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354071</v>
+        <v>121354501</v>
       </c>
       <c r="B3" t="n">
-        <v>79216</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571522</v>
+        <v>571517</v>
       </c>
       <c r="R3" t="n">
-        <v>6450409</v>
+        <v>6450430</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354501</v>
+        <v>121355319</v>
       </c>
       <c r="B4" t="n">
-        <v>57364</v>
+        <v>90717</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,39 +915,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571517</v>
+        <v>571530</v>
       </c>
       <c r="R4" t="n">
-        <v>6450430</v>
+        <v>6450425</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,6 +990,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354089</v>
+        <v>121355322</v>
       </c>
       <c r="B5" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571517</v>
+        <v>571482</v>
       </c>
       <c r="R5" t="n">
-        <v>6450391</v>
+        <v>6450443</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354069</v>
+        <v>121354071</v>
       </c>
       <c r="B6" t="n">
-        <v>78243</v>
+        <v>79219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571526</v>
+        <v>571522</v>
       </c>
       <c r="R6" t="n">
-        <v>6450419</v>
+        <v>6450409</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121355329</v>
+        <v>121354089</v>
       </c>
       <c r="B7" t="n">
-        <v>57501</v>
+        <v>79219</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,35 +1237,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571457</v>
+        <v>571517</v>
       </c>
       <c r="R7" t="n">
-        <v>6450480</v>
+        <v>6450391</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1307,17 +1302,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1336,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121355319</v>
+        <v>121354069</v>
       </c>
       <c r="B8" t="n">
-        <v>90707</v>
+        <v>78246</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,28 +1343,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1383,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571530</v>
+        <v>571526</v>
       </c>
       <c r="R8" t="n">
-        <v>6450425</v>
+        <v>6450419</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354693</v>
+        <v>121355329</v>
       </c>
       <c r="B9" t="n">
-        <v>79216</v>
+        <v>57504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,26 +1449,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1489,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571533</v>
+        <v>571457</v>
       </c>
       <c r="R9" t="n">
-        <v>6450433</v>
+        <v>6450480</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1527,13 +1523,17 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354845</v>
+        <v>121354693</v>
       </c>
       <c r="B10" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571550</v>
+        <v>571533</v>
       </c>
       <c r="R10" t="n">
-        <v>6450420</v>
+        <v>6450433</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1661,7 +1661,7 @@
         <v>121354064</v>
       </c>
       <c r="B11" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121355322</v>
+        <v>121354845</v>
       </c>
       <c r="B12" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571482</v>
+        <v>571550</v>
       </c>
       <c r="R12" t="n">
-        <v>6450443</v>
+        <v>6450420</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 58169-2023 artfynd.xlsx
+++ b/artfynd/A 58169-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354996</v>
+        <v>121355322</v>
       </c>
       <c r="B2" t="n">
         <v>79219</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571569</v>
+        <v>571482</v>
       </c>
       <c r="R2" t="n">
-        <v>6450396</v>
+        <v>6450443</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354501</v>
+        <v>121354845</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>79219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,39 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571517</v>
+        <v>571550</v>
       </c>
       <c r="R3" t="n">
-        <v>6450430</v>
+        <v>6450420</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1009,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121355322</v>
+        <v>121354089</v>
       </c>
       <c r="B5" t="n">
         <v>79219</v>
@@ -1052,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571482</v>
+        <v>571517</v>
       </c>
       <c r="R5" t="n">
-        <v>6450443</v>
+        <v>6450391</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354071</v>
+        <v>121354064</v>
       </c>
       <c r="B6" t="n">
         <v>79219</v>
@@ -1158,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571522</v>
+        <v>571546</v>
       </c>
       <c r="R6" t="n">
-        <v>6450409</v>
+        <v>6450385</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354089</v>
+        <v>121354501</v>
       </c>
       <c r="B7" t="n">
-        <v>79219</v>
+        <v>57367</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,26 +1225,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1267,7 +1268,7 @@
         <v>571517</v>
       </c>
       <c r="R7" t="n">
-        <v>6450391</v>
+        <v>6450430</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,7 +1309,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354069</v>
+        <v>121355329</v>
       </c>
       <c r="B8" t="n">
-        <v>78246</v>
+        <v>57504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,26 +1343,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1370,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571526</v>
+        <v>571457</v>
       </c>
       <c r="R8" t="n">
-        <v>6450419</v>
+        <v>6450480</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1408,13 +1417,17 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1433,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121355329</v>
+        <v>121354996</v>
       </c>
       <c r="B9" t="n">
-        <v>57504</v>
+        <v>79219</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,35 +1462,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1485,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571457</v>
+        <v>571569</v>
       </c>
       <c r="R9" t="n">
-        <v>6450480</v>
+        <v>6450396</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,17 +1527,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354064</v>
+        <v>121354071</v>
       </c>
       <c r="B11" t="n">
         <v>79219</v>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571546</v>
+        <v>571522</v>
       </c>
       <c r="R11" t="n">
-        <v>6450385</v>
+        <v>6450409</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354845</v>
+        <v>121354069</v>
       </c>
       <c r="B12" t="n">
-        <v>79219</v>
+        <v>78246</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,21 +1780,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571550</v>
+        <v>571526</v>
       </c>
       <c r="R12" t="n">
-        <v>6450420</v>
+        <v>6450419</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 58169-2023 artfynd.xlsx
+++ b/artfynd/A 58169-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121355322</v>
+        <v>121354089</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571482</v>
+        <v>571517</v>
       </c>
       <c r="R2" t="n">
-        <v>6450443</v>
+        <v>6450391</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354845</v>
+        <v>121354996</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571550</v>
+        <v>571569</v>
       </c>
       <c r="R3" t="n">
-        <v>6450420</v>
+        <v>6450396</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355319</v>
+        <v>121354064</v>
       </c>
       <c r="B4" t="n">
-        <v>90717</v>
+        <v>79222</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,28 +903,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -934,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571530</v>
+        <v>571546</v>
       </c>
       <c r="R4" t="n">
-        <v>6450425</v>
+        <v>6450385</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354089</v>
+        <v>121354069</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>78249</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571517</v>
+        <v>571526</v>
       </c>
       <c r="R5" t="n">
-        <v>6450391</v>
+        <v>6450419</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354064</v>
+        <v>121354501</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>57367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,26 +1115,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1146,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571546</v>
+        <v>571517</v>
       </c>
       <c r="R6" t="n">
-        <v>6450385</v>
+        <v>6450430</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,7 +1199,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1209,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354501</v>
+        <v>121355322</v>
       </c>
       <c r="B7" t="n">
-        <v>57367</v>
+        <v>79222</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,39 +1233,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1265,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571517</v>
+        <v>571482</v>
       </c>
       <c r="R7" t="n">
-        <v>6450430</v>
+        <v>6450443</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1309,6 +1304,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1446,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354996</v>
+        <v>121354693</v>
       </c>
       <c r="B9" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571569</v>
+        <v>571533</v>
       </c>
       <c r="R9" t="n">
-        <v>6450396</v>
+        <v>6450433</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1552,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354693</v>
+        <v>121354071</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571533</v>
+        <v>571522</v>
       </c>
       <c r="R10" t="n">
-        <v>6450433</v>
+        <v>6450409</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1658,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354071</v>
+        <v>121354845</v>
       </c>
       <c r="B11" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571522</v>
+        <v>571550</v>
       </c>
       <c r="R11" t="n">
-        <v>6450409</v>
+        <v>6450420</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1764,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354069</v>
+        <v>121355319</v>
       </c>
       <c r="B12" t="n">
-        <v>78246</v>
+        <v>90729</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,24 +1776,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571526</v>
+        <v>571530</v>
       </c>
       <c r="R12" t="n">
-        <v>6450419</v>
+        <v>6450425</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 58169-2023 artfynd.xlsx
+++ b/artfynd/A 58169-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354089</v>
+        <v>121354071</v>
       </c>
       <c r="B2" t="n">
         <v>79222</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571517</v>
+        <v>571522</v>
       </c>
       <c r="R2" t="n">
-        <v>6450391</v>
+        <v>6450409</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354996</v>
+        <v>121354069</v>
       </c>
       <c r="B3" t="n">
-        <v>79222</v>
+        <v>78249</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571569</v>
+        <v>571526</v>
       </c>
       <c r="R3" t="n">
-        <v>6450396</v>
+        <v>6450419</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354064</v>
+        <v>121355319</v>
       </c>
       <c r="B4" t="n">
-        <v>79222</v>
+        <v>90730</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,24 +903,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -930,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571546</v>
+        <v>571530</v>
       </c>
       <c r="R4" t="n">
-        <v>6450385</v>
+        <v>6450425</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354069</v>
+        <v>121355329</v>
       </c>
       <c r="B5" t="n">
-        <v>78249</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,26 +1013,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571526</v>
+        <v>571457</v>
       </c>
       <c r="R5" t="n">
-        <v>6450419</v>
+        <v>6450480</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1074,13 +1087,17 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1217,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121355322</v>
+        <v>121354996</v>
       </c>
       <c r="B7" t="n">
         <v>79222</v>
@@ -1260,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571482</v>
+        <v>571569</v>
       </c>
       <c r="R7" t="n">
-        <v>6450443</v>
+        <v>6450396</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1323,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121355329</v>
+        <v>121354089</v>
       </c>
       <c r="B8" t="n">
-        <v>57504</v>
+        <v>79222</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,35 +1356,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571457</v>
+        <v>571517</v>
       </c>
       <c r="R8" t="n">
-        <v>6450480</v>
+        <v>6450391</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1413,17 +1421,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1442,7 +1446,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354693</v>
+        <v>121354845</v>
       </c>
       <c r="B9" t="n">
         <v>79222</v>
@@ -1485,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571533</v>
+        <v>571550</v>
       </c>
       <c r="R9" t="n">
-        <v>6450433</v>
+        <v>6450420</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1548,7 +1552,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354071</v>
+        <v>121354693</v>
       </c>
       <c r="B10" t="n">
         <v>79222</v>
@@ -1591,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571522</v>
+        <v>571533</v>
       </c>
       <c r="R10" t="n">
-        <v>6450409</v>
+        <v>6450433</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,7 +1658,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354845</v>
+        <v>121354064</v>
       </c>
       <c r="B11" t="n">
         <v>79222</v>
@@ -1697,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571550</v>
+        <v>571546</v>
       </c>
       <c r="R11" t="n">
-        <v>6450420</v>
+        <v>6450385</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121355319</v>
+        <v>121355322</v>
       </c>
       <c r="B12" t="n">
-        <v>90729</v>
+        <v>79222</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,28 +1780,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571530</v>
+        <v>571482</v>
       </c>
       <c r="R12" t="n">
-        <v>6450425</v>
+        <v>6450443</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 58169-2023 artfynd.xlsx
+++ b/artfynd/A 58169-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121354071</v>
       </c>
       <c r="B2" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354069</v>
+        <v>121355329</v>
       </c>
       <c r="B3" t="n">
-        <v>78249</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571526</v>
+        <v>571457</v>
       </c>
       <c r="R3" t="n">
-        <v>6450419</v>
+        <v>6450480</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,13 +871,17 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355319</v>
+        <v>121354693</v>
       </c>
       <c r="B4" t="n">
-        <v>90730</v>
+        <v>79225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,28 +916,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -934,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571530</v>
+        <v>571533</v>
       </c>
       <c r="R4" t="n">
-        <v>6450425</v>
+        <v>6450433</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121355329</v>
+        <v>121354064</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>79225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,35 +1022,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571457</v>
+        <v>571546</v>
       </c>
       <c r="R5" t="n">
-        <v>6450480</v>
+        <v>6450385</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,17 +1087,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1116,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354501</v>
+        <v>121354069</v>
       </c>
       <c r="B6" t="n">
-        <v>57367</v>
+        <v>78252</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,39 +1128,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1172,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571517</v>
+        <v>571526</v>
       </c>
       <c r="R6" t="n">
-        <v>6450430</v>
+        <v>6450419</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,6 +1199,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1234,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354996</v>
+        <v>121354089</v>
       </c>
       <c r="B7" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571569</v>
+        <v>571517</v>
       </c>
       <c r="R7" t="n">
-        <v>6450396</v>
+        <v>6450391</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1340,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354089</v>
+        <v>121355322</v>
       </c>
       <c r="B8" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571517</v>
+        <v>571482</v>
       </c>
       <c r="R8" t="n">
-        <v>6450391</v>
+        <v>6450443</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1449,7 +1433,7 @@
         <v>121354845</v>
       </c>
       <c r="B9" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1552,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354693</v>
+        <v>121354996</v>
       </c>
       <c r="B10" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571533</v>
+        <v>571569</v>
       </c>
       <c r="R10" t="n">
-        <v>6450433</v>
+        <v>6450396</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1658,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354064</v>
+        <v>121355319</v>
       </c>
       <c r="B11" t="n">
-        <v>79222</v>
+        <v>90733</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,24 +1658,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1701,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571546</v>
+        <v>571530</v>
       </c>
       <c r="R11" t="n">
-        <v>6450385</v>
+        <v>6450425</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1764,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121355322</v>
+        <v>121354501</v>
       </c>
       <c r="B12" t="n">
-        <v>79222</v>
+        <v>57370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,26 +1768,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1807,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571482</v>
+        <v>571517</v>
       </c>
       <c r="R12" t="n">
-        <v>6450443</v>
+        <v>6450430</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1851,7 +1852,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58169-2023 artfynd.xlsx
+++ b/artfynd/A 58169-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354071</v>
+        <v>121355322</v>
       </c>
       <c r="B2" t="n">
         <v>79225</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571522</v>
+        <v>571482</v>
       </c>
       <c r="R2" t="n">
-        <v>6450409</v>
+        <v>6450443</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121355329</v>
+        <v>121354845</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>79225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571457</v>
+        <v>571550</v>
       </c>
       <c r="R3" t="n">
-        <v>6450480</v>
+        <v>6450420</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,17 +862,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354693</v>
+        <v>121355329</v>
       </c>
       <c r="B4" t="n">
-        <v>79225</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,26 +903,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571533</v>
+        <v>571457</v>
       </c>
       <c r="R4" t="n">
-        <v>6450433</v>
+        <v>6450480</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,13 +977,17 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1006,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354064</v>
+        <v>121354693</v>
       </c>
       <c r="B5" t="n">
         <v>79225</v>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571546</v>
+        <v>571533</v>
       </c>
       <c r="R5" t="n">
-        <v>6450385</v>
+        <v>6450433</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354069</v>
+        <v>121354501</v>
       </c>
       <c r="B6" t="n">
-        <v>78252</v>
+        <v>57370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,26 +1128,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571526</v>
+        <v>571517</v>
       </c>
       <c r="R6" t="n">
-        <v>6450419</v>
+        <v>6450430</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,7 +1212,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1218,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354089</v>
+        <v>121354071</v>
       </c>
       <c r="B7" t="n">
         <v>79225</v>
@@ -1261,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571517</v>
+        <v>571522</v>
       </c>
       <c r="R7" t="n">
-        <v>6450391</v>
+        <v>6450409</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1324,7 +1336,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121355322</v>
+        <v>121354064</v>
       </c>
       <c r="B8" t="n">
         <v>79225</v>
@@ -1367,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571482</v>
+        <v>571546</v>
       </c>
       <c r="R8" t="n">
-        <v>6450443</v>
+        <v>6450385</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1430,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354845</v>
+        <v>121355319</v>
       </c>
       <c r="B9" t="n">
-        <v>79225</v>
+        <v>90733</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,24 +1458,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1473,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571550</v>
+        <v>571530</v>
       </c>
       <c r="R9" t="n">
-        <v>6450420</v>
+        <v>6450425</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1642,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121355319</v>
+        <v>121354089</v>
       </c>
       <c r="B11" t="n">
-        <v>90733</v>
+        <v>79225</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,28 +1674,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1689,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571530</v>
+        <v>571517</v>
       </c>
       <c r="R11" t="n">
-        <v>6450425</v>
+        <v>6450391</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1752,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354501</v>
+        <v>121354069</v>
       </c>
       <c r="B12" t="n">
-        <v>57370</v>
+        <v>78252</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,39 +1780,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1808,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571517</v>
+        <v>571526</v>
       </c>
       <c r="R12" t="n">
-        <v>6450430</v>
+        <v>6450419</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1852,6 +1851,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58169-2023 artfynd.xlsx
+++ b/artfynd/A 58169-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121355322</v>
+        <v>121354996</v>
       </c>
       <c r="B2" t="n">
-        <v>79225</v>
+        <v>79226</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571482</v>
+        <v>571569</v>
       </c>
       <c r="R2" t="n">
-        <v>6450443</v>
+        <v>6450396</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -784,7 +784,7 @@
         <v>121354845</v>
       </c>
       <c r="B3" t="n">
-        <v>79225</v>
+        <v>79226</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355329</v>
+        <v>121354693</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>79226</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,35 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571457</v>
+        <v>571533</v>
       </c>
       <c r="R4" t="n">
-        <v>6450480</v>
+        <v>6450433</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,17 +968,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1006,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354693</v>
+        <v>121354089</v>
       </c>
       <c r="B5" t="n">
-        <v>79225</v>
+        <v>79226</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571533</v>
+        <v>571517</v>
       </c>
       <c r="R5" t="n">
-        <v>6450433</v>
+        <v>6450391</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354501</v>
+        <v>121355319</v>
       </c>
       <c r="B6" t="n">
-        <v>57370</v>
+        <v>90739</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,39 +1115,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1168,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571517</v>
+        <v>571530</v>
       </c>
       <c r="R6" t="n">
-        <v>6450430</v>
+        <v>6450425</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,6 +1190,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1230,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354071</v>
+        <v>121354069</v>
       </c>
       <c r="B7" t="n">
-        <v>79225</v>
+        <v>78253</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1273,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571522</v>
+        <v>571526</v>
       </c>
       <c r="R7" t="n">
-        <v>6450409</v>
+        <v>6450419</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1336,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354064</v>
+        <v>121354071</v>
       </c>
       <c r="B8" t="n">
-        <v>79225</v>
+        <v>79226</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571546</v>
+        <v>571522</v>
       </c>
       <c r="R8" t="n">
-        <v>6450385</v>
+        <v>6450409</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1442,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121355319</v>
+        <v>121354501</v>
       </c>
       <c r="B9" t="n">
-        <v>90733</v>
+        <v>57371</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,30 +1437,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1489,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571530</v>
+        <v>571517</v>
       </c>
       <c r="R9" t="n">
-        <v>6450425</v>
+        <v>6450430</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,7 +1521,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1552,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354996</v>
+        <v>121355322</v>
       </c>
       <c r="B10" t="n">
-        <v>79225</v>
+        <v>79226</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571569</v>
+        <v>571482</v>
       </c>
       <c r="R10" t="n">
-        <v>6450396</v>
+        <v>6450443</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1658,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354089</v>
+        <v>121355329</v>
       </c>
       <c r="B11" t="n">
-        <v>79225</v>
+        <v>57508</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,26 +1661,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1701,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571517</v>
+        <v>571457</v>
       </c>
       <c r="R11" t="n">
-        <v>6450391</v>
+        <v>6450480</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1739,13 +1735,17 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354069</v>
+        <v>121354064</v>
       </c>
       <c r="B12" t="n">
-        <v>78252</v>
+        <v>79226</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,21 +1780,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571526</v>
+        <v>571546</v>
       </c>
       <c r="R12" t="n">
-        <v>6450419</v>
+        <v>6450385</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 58169-2023 artfynd.xlsx
+++ b/artfynd/A 58169-2023 artfynd.xlsx
@@ -1421,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354501</v>
+        <v>121355322</v>
       </c>
       <c r="B9" t="n">
-        <v>57371</v>
+        <v>79226</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,39 +1437,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1477,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571517</v>
+        <v>571482</v>
       </c>
       <c r="R9" t="n">
-        <v>6450430</v>
+        <v>6450443</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1521,6 +1508,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1539,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121355322</v>
+        <v>121354501</v>
       </c>
       <c r="B10" t="n">
-        <v>79226</v>
+        <v>57371</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,26 +1543,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1582,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571482</v>
+        <v>571517</v>
       </c>
       <c r="R10" t="n">
-        <v>6450443</v>
+        <v>6450430</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1626,7 +1627,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58169-2023 artfynd.xlsx
+++ b/artfynd/A 58169-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354996</v>
+        <v>121354071</v>
       </c>
       <c r="B2" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571569</v>
+        <v>571522</v>
       </c>
       <c r="R2" t="n">
-        <v>6450396</v>
+        <v>6450409</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354845</v>
+        <v>121354069</v>
       </c>
       <c r="B3" t="n">
-        <v>79226</v>
+        <v>78254</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571550</v>
+        <v>571526</v>
       </c>
       <c r="R3" t="n">
-        <v>6450420</v>
+        <v>6450419</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354693</v>
+        <v>121355322</v>
       </c>
       <c r="B4" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571533</v>
+        <v>571482</v>
       </c>
       <c r="R4" t="n">
-        <v>6450433</v>
+        <v>6450443</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354089</v>
+        <v>121354693</v>
       </c>
       <c r="B5" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571517</v>
+        <v>571533</v>
       </c>
       <c r="R5" t="n">
-        <v>6450391</v>
+        <v>6450433</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121355319</v>
+        <v>121354845</v>
       </c>
       <c r="B6" t="n">
-        <v>90739</v>
+        <v>79227</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,28 +1115,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1146,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571530</v>
+        <v>571550</v>
       </c>
       <c r="R6" t="n">
-        <v>6450425</v>
+        <v>6450420</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354069</v>
+        <v>121354996</v>
       </c>
       <c r="B7" t="n">
-        <v>78253</v>
+        <v>79227</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571526</v>
+        <v>571569</v>
       </c>
       <c r="R7" t="n">
-        <v>6450419</v>
+        <v>6450396</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1315,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354071</v>
+        <v>121355319</v>
       </c>
       <c r="B8" t="n">
-        <v>79226</v>
+        <v>90740</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,24 +1327,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571522</v>
+        <v>571530</v>
       </c>
       <c r="R8" t="n">
-        <v>6450409</v>
+        <v>6450425</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1421,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121355322</v>
+        <v>121354089</v>
       </c>
       <c r="B9" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571482</v>
+        <v>571517</v>
       </c>
       <c r="R9" t="n">
-        <v>6450443</v>
+        <v>6450391</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1527,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354501</v>
+        <v>121354064</v>
       </c>
       <c r="B10" t="n">
-        <v>57371</v>
+        <v>79227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,39 +1543,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1583,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571517</v>
+        <v>571546</v>
       </c>
       <c r="R10" t="n">
-        <v>6450430</v>
+        <v>6450385</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1627,6 +1614,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1648,7 +1636,7 @@
         <v>121355329</v>
       </c>
       <c r="B11" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354064</v>
+        <v>121354501</v>
       </c>
       <c r="B12" t="n">
-        <v>79226</v>
+        <v>57372</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,26 +1768,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1807,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571546</v>
+        <v>571517</v>
       </c>
       <c r="R12" t="n">
-        <v>6450385</v>
+        <v>6450430</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1851,7 +1852,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58169-2023 artfynd.xlsx
+++ b/artfynd/A 58169-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354071</v>
+        <v>121355319</v>
       </c>
       <c r="B2" t="n">
-        <v>79227</v>
+        <v>90740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,24 +691,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571522</v>
+        <v>571530</v>
       </c>
       <c r="R2" t="n">
-        <v>6450409</v>
+        <v>6450425</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354069</v>
+        <v>121355322</v>
       </c>
       <c r="B3" t="n">
-        <v>78254</v>
+        <v>79227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571526</v>
+        <v>571482</v>
       </c>
       <c r="R3" t="n">
-        <v>6450419</v>
+        <v>6450443</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,7 +891,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121355322</v>
+        <v>121354071</v>
       </c>
       <c r="B4" t="n">
         <v>79227</v>
@@ -930,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571482</v>
+        <v>571522</v>
       </c>
       <c r="R4" t="n">
-        <v>6450443</v>
+        <v>6450409</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354693</v>
+        <v>121354089</v>
       </c>
       <c r="B5" t="n">
         <v>79227</v>
@@ -1036,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571533</v>
+        <v>571517</v>
       </c>
       <c r="R5" t="n">
-        <v>6450433</v>
+        <v>6450391</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354845</v>
+        <v>121354693</v>
       </c>
       <c r="B6" t="n">
         <v>79227</v>
@@ -1142,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571550</v>
+        <v>571533</v>
       </c>
       <c r="R6" t="n">
-        <v>6450420</v>
+        <v>6450433</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354996</v>
+        <v>121354064</v>
       </c>
       <c r="B7" t="n">
         <v>79227</v>
@@ -1248,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571569</v>
+        <v>571546</v>
       </c>
       <c r="R7" t="n">
-        <v>6450396</v>
+        <v>6450385</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121355319</v>
+        <v>121354069</v>
       </c>
       <c r="B8" t="n">
-        <v>90740</v>
+        <v>78254</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,28 +1331,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571530</v>
+        <v>571526</v>
       </c>
       <c r="R8" t="n">
-        <v>6450425</v>
+        <v>6450419</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354089</v>
+        <v>121354845</v>
       </c>
       <c r="B9" t="n">
         <v>79227</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571517</v>
+        <v>571550</v>
       </c>
       <c r="R9" t="n">
-        <v>6450391</v>
+        <v>6450420</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1527,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354064</v>
+        <v>121354501</v>
       </c>
       <c r="B10" t="n">
-        <v>79227</v>
+        <v>57372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,26 +1543,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1570,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571546</v>
+        <v>571517</v>
       </c>
       <c r="R10" t="n">
-        <v>6450385</v>
+        <v>6450430</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1614,7 +1627,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1633,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121355329</v>
+        <v>121354996</v>
       </c>
       <c r="B11" t="n">
-        <v>57509</v>
+        <v>79227</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,35 +1661,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1685,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571457</v>
+        <v>571569</v>
       </c>
       <c r="R11" t="n">
-        <v>6450480</v>
+        <v>6450396</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1723,17 +1726,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1752,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354501</v>
+        <v>121355329</v>
       </c>
       <c r="B12" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,37 +1767,33 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1808,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571517</v>
+        <v>571457</v>
       </c>
       <c r="R12" t="n">
-        <v>6450430</v>
+        <v>6450480</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1844,6 +1839,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 58169-2023 artfynd.xlsx
+++ b/artfynd/A 58169-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121355319</v>
+        <v>121354089</v>
       </c>
       <c r="B2" t="n">
-        <v>90740</v>
+        <v>79227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,28 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571530</v>
+        <v>571517</v>
       </c>
       <c r="R2" t="n">
-        <v>6450425</v>
+        <v>6450391</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -785,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121355322</v>
+        <v>121354064</v>
       </c>
       <c r="B3" t="n">
         <v>79227</v>
@@ -828,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571482</v>
+        <v>571546</v>
       </c>
       <c r="R3" t="n">
-        <v>6450443</v>
+        <v>6450385</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -997,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354089</v>
+        <v>121354069</v>
       </c>
       <c r="B5" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571517</v>
+        <v>571526</v>
       </c>
       <c r="R5" t="n">
-        <v>6450391</v>
+        <v>6450419</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354693</v>
+        <v>121355319</v>
       </c>
       <c r="B6" t="n">
-        <v>79227</v>
+        <v>90740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,24 +1115,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571533</v>
+        <v>571530</v>
       </c>
       <c r="R6" t="n">
-        <v>6450433</v>
+        <v>6450425</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354064</v>
+        <v>121354693</v>
       </c>
       <c r="B7" t="n">
         <v>79227</v>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571546</v>
+        <v>571533</v>
       </c>
       <c r="R7" t="n">
-        <v>6450385</v>
+        <v>6450433</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354069</v>
+        <v>121354845</v>
       </c>
       <c r="B8" t="n">
-        <v>78254</v>
+        <v>79227</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,21 +1331,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571526</v>
+        <v>571550</v>
       </c>
       <c r="R8" t="n">
-        <v>6450419</v>
+        <v>6450420</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1421,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354845</v>
+        <v>121354501</v>
       </c>
       <c r="B9" t="n">
-        <v>79227</v>
+        <v>57372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,26 +1437,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1464,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571550</v>
+        <v>571517</v>
       </c>
       <c r="R9" t="n">
-        <v>6450420</v>
+        <v>6450430</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1508,7 +1521,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1527,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354501</v>
+        <v>121354996</v>
       </c>
       <c r="B10" t="n">
-        <v>57372</v>
+        <v>79227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,39 +1555,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1583,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571517</v>
+        <v>571569</v>
       </c>
       <c r="R10" t="n">
-        <v>6450430</v>
+        <v>6450396</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1627,6 +1626,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354996</v>
+        <v>121355322</v>
       </c>
       <c r="B11" t="n">
         <v>79227</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571569</v>
+        <v>571482</v>
       </c>
       <c r="R11" t="n">
-        <v>6450396</v>
+        <v>6450443</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 58169-2023 artfynd.xlsx
+++ b/artfynd/A 58169-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354089</v>
+        <v>121354501</v>
       </c>
       <c r="B2" t="n">
-        <v>79227</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,7 +734,7 @@
         <v>571517</v>
       </c>
       <c r="R2" t="n">
-        <v>6450391</v>
+        <v>6450430</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +775,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354064</v>
+        <v>121354996</v>
       </c>
       <c r="B3" t="n">
         <v>79227</v>
@@ -824,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571546</v>
+        <v>571569</v>
       </c>
       <c r="R3" t="n">
-        <v>6450385</v>
+        <v>6450396</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354071</v>
+        <v>121354089</v>
       </c>
       <c r="B4" t="n">
         <v>79227</v>
@@ -930,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571522</v>
+        <v>571517</v>
       </c>
       <c r="R4" t="n">
-        <v>6450409</v>
+        <v>6450391</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354069</v>
+        <v>121354071</v>
       </c>
       <c r="B5" t="n">
-        <v>78254</v>
+        <v>79227</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571526</v>
+        <v>571522</v>
       </c>
       <c r="R5" t="n">
-        <v>6450419</v>
+        <v>6450409</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121355319</v>
+        <v>121354064</v>
       </c>
       <c r="B6" t="n">
-        <v>90740</v>
+        <v>79227</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,28 +1127,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1146,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571530</v>
+        <v>571546</v>
       </c>
       <c r="R6" t="n">
-        <v>6450425</v>
+        <v>6450385</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354693</v>
+        <v>121355319</v>
       </c>
       <c r="B7" t="n">
-        <v>79227</v>
+        <v>90740</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,24 +1233,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1252,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571533</v>
+        <v>571530</v>
       </c>
       <c r="R7" t="n">
-        <v>6450433</v>
+        <v>6450425</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1315,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354845</v>
+        <v>121354069</v>
       </c>
       <c r="B8" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1358,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571550</v>
+        <v>571526</v>
       </c>
       <c r="R8" t="n">
-        <v>6450420</v>
+        <v>6450419</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1421,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354501</v>
+        <v>121354845</v>
       </c>
       <c r="B9" t="n">
-        <v>57372</v>
+        <v>79227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,39 +1449,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1477,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571517</v>
+        <v>571550</v>
       </c>
       <c r="R9" t="n">
-        <v>6450430</v>
+        <v>6450420</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1521,6 +1520,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354996</v>
+        <v>121355329</v>
       </c>
       <c r="B10" t="n">
-        <v>79227</v>
+        <v>57509</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,26 +1555,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1582,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571569</v>
+        <v>571457</v>
       </c>
       <c r="R10" t="n">
-        <v>6450396</v>
+        <v>6450480</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1620,13 +1629,17 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1751,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121355329</v>
+        <v>121354693</v>
       </c>
       <c r="B12" t="n">
-        <v>57509</v>
+        <v>79227</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,35 +1780,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1803,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571457</v>
+        <v>571533</v>
       </c>
       <c r="R12" t="n">
-        <v>6450480</v>
+        <v>6450433</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,17 +1845,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58169-2023 artfynd.xlsx
+++ b/artfynd/A 58169-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354501</v>
+        <v>121354693</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>79234</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571517</v>
+        <v>571533</v>
       </c>
       <c r="R2" t="n">
-        <v>6450430</v>
+        <v>6450433</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354996</v>
+        <v>121354501</v>
       </c>
       <c r="B3" t="n">
-        <v>79227</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,26 +797,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571569</v>
+        <v>571517</v>
       </c>
       <c r="R3" t="n">
-        <v>6450396</v>
+        <v>6450430</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,7 +902,7 @@
         <v>121354089</v>
       </c>
       <c r="B4" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>121354071</v>
       </c>
       <c r="B5" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354064</v>
+        <v>121355322</v>
       </c>
       <c r="B6" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571546</v>
+        <v>571482</v>
       </c>
       <c r="R6" t="n">
-        <v>6450385</v>
+        <v>6450443</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121355319</v>
+        <v>121355329</v>
       </c>
       <c r="B7" t="n">
-        <v>90740</v>
+        <v>57510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,30 +1233,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1264,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571530</v>
+        <v>571457</v>
       </c>
       <c r="R7" t="n">
-        <v>6450425</v>
+        <v>6450480</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1302,13 +1307,17 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1327,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354069</v>
+        <v>121355319</v>
       </c>
       <c r="B8" t="n">
-        <v>78254</v>
+        <v>90748</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,24 +1352,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1370,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571526</v>
+        <v>571530</v>
       </c>
       <c r="R8" t="n">
-        <v>6450419</v>
+        <v>6450425</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1436,7 +1449,7 @@
         <v>121354845</v>
       </c>
       <c r="B9" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121355329</v>
+        <v>121354069</v>
       </c>
       <c r="B10" t="n">
-        <v>57509</v>
+        <v>78261</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,35 +1568,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1591,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571457</v>
+        <v>571526</v>
       </c>
       <c r="R10" t="n">
-        <v>6450480</v>
+        <v>6450419</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,17 +1633,13 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Förälderns med tre av årets ungar I sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121355322</v>
+        <v>121354064</v>
       </c>
       <c r="B11" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571482</v>
+        <v>571546</v>
       </c>
       <c r="R11" t="n">
-        <v>6450443</v>
+        <v>6450385</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354693</v>
+        <v>121354996</v>
       </c>
       <c r="B12" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571533</v>
+        <v>571569</v>
       </c>
       <c r="R12" t="n">
-        <v>6450433</v>
+        <v>6450396</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
